--- a/exit_interview_templates/043_exit_interview_authorization_form--exit_interview_templates.xlsx
+++ b/exit_interview_templates/043_exit_interview_authorization_form--exit_interview_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'what_were_some_of_the_most_significant_reasons_why_you_are_leaving?'}</t>
+          <t>what_were_some_of_the_most_significant_reasons_why_you_are_leaving?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'What were some of the most significant reasons why you are leaving?'}</t>
+          <t>What were some of the most significant reasons why you are leaving?</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"how_do_you_rate_your_manager's_management_style?"}</t>
+          <t>how_do_you_rate_your_manager's_management_style?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "How do you rate your manager's management style?"}</t>
+          <t>How do you rate your manager's management style?</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'what_suggestions_do_you_have_for_improving_our_workplace_culture?'}</t>
+          <t>what_suggestions_do_you_have_for_improving_our_workplace_culture?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'What suggestions do you have for improving our workplace culture?'}</t>
+          <t>What suggestions do you have for improving our workplace culture?</t>
         </is>
       </c>
     </row>
